--- a/output/roomself_excel/12102.xlsx
+++ b/output/roomself_excel/12102.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>844911</v>
+        <v>219099</v>
       </c>
       <c r="D2" t="n">
-        <v>13340</v>
+        <v>3816</v>
       </c>
       <c r="E2" t="n">
-        <v>1246</v>
+        <v>739</v>
       </c>
       <c r="F2" t="n">
-        <v>1112</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>135891</v>
+        <v>441688</v>
       </c>
       <c r="D3" t="n">
-        <v>3092</v>
+        <v>6700</v>
       </c>
       <c r="E3" t="n">
-        <v>641</v>
+        <v>1034</v>
       </c>
       <c r="F3" t="n">
-        <v>266</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>59409</v>
+        <v>144216</v>
       </c>
       <c r="D4" t="n">
-        <v>1976</v>
+        <v>3148</v>
       </c>
       <c r="E4" t="n">
-        <v>332</v>
+        <v>505</v>
       </c>
       <c r="F4" t="n">
-        <v>248</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>66138</v>
+        <v>147735</v>
       </c>
       <c r="D5" t="n">
-        <v>2396</v>
+        <v>3136</v>
       </c>
       <c r="E5" t="n">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="F5" t="n">
-        <v>161</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>289620</v>
+        <v>145557</v>
       </c>
       <c r="D6" t="n">
-        <v>5952</v>
+        <v>3180</v>
       </c>
       <c r="E6" t="n">
-        <v>1011</v>
+        <v>508</v>
       </c>
       <c r="F6" t="n">
-        <v>755</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>144216</v>
+        <v>144849</v>
       </c>
       <c r="D7" t="n">
-        <v>3148</v>
+        <v>3116</v>
       </c>
       <c r="E7" t="n">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="F7" t="n">
         <v>490</v>
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>147735</v>
+        <v>61325</v>
       </c>
       <c r="D8" t="n">
-        <v>3136</v>
+        <v>1992</v>
       </c>
       <c r="E8" t="n">
-        <v>515</v>
+        <v>223</v>
       </c>
       <c r="F8" t="n">
-        <v>508</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>61325</v>
+        <v>30207</v>
       </c>
       <c r="D9" t="n">
-        <v>1992</v>
+        <v>1424</v>
       </c>
       <c r="E9" t="n">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23790</v>
+        <v>34965</v>
       </c>
       <c r="D10" t="n">
-        <v>1268</v>
+        <v>1536</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20008</v>
+        <v>34965</v>
       </c>
       <c r="D11" t="n">
-        <v>1144</v>
+        <v>1576</v>
       </c>
       <c r="E11" t="n">
-        <v>122</v>
+        <v>289</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>145557</v>
+        <v>184124</v>
       </c>
       <c r="D12" t="n">
-        <v>3180</v>
+        <v>5520</v>
       </c>
       <c r="E12" t="n">
-        <v>508</v>
+        <v>370</v>
       </c>
       <c r="F12" t="n">
-        <v>505</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>144849</v>
+        <v>23790</v>
       </c>
       <c r="D13" t="n">
-        <v>3116</v>
+        <v>1268</v>
       </c>
       <c r="E13" t="n">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>124033</v>
+        <v>29016</v>
       </c>
       <c r="D14" t="n">
-        <v>2824</v>
+        <v>1432</v>
       </c>
       <c r="E14" t="n">
-        <v>422</v>
+        <v>124</v>
       </c>
       <c r="F14" t="n">
-        <v>383</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30207</v>
+        <v>164352</v>
       </c>
       <c r="D15" t="n">
-        <v>1424</v>
+        <v>3928</v>
       </c>
       <c r="E15" t="n">
-        <v>270</v>
+        <v>830</v>
       </c>
       <c r="F15" t="n">
-        <v>141</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29016</v>
+        <v>68471</v>
       </c>
       <c r="D16" t="n">
-        <v>1432</v>
+        <v>2112</v>
       </c>
       <c r="E16" t="n">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>34965</v>
+        <v>552192</v>
       </c>
       <c r="D17" t="n">
-        <v>1536</v>
+        <v>5948</v>
       </c>
       <c r="E17" t="n">
-        <v>180</v>
+        <v>830</v>
       </c>
       <c r="F17" t="n">
-        <v>150</v>
+        <v>719</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>66670</v>
+        <v>135891</v>
       </c>
       <c r="D18" t="n">
-        <v>2400</v>
+        <v>3092</v>
       </c>
       <c r="E18" t="n">
-        <v>475</v>
+        <v>641</v>
       </c>
       <c r="F18" t="n">
-        <v>163</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>59430</v>
+        <v>59409</v>
       </c>
       <c r="D19" t="n">
-        <v>2324</v>
+        <v>1976</v>
       </c>
       <c r="E19" t="n">
-        <v>493</v>
+        <v>332</v>
       </c>
       <c r="F19" t="n">
-        <v>181</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>203712</v>
+        <v>66138</v>
       </c>
       <c r="D20" t="n">
-        <v>4172</v>
+        <v>2396</v>
       </c>
       <c r="E20" t="n">
-        <v>651</v>
+        <v>483</v>
       </c>
       <c r="F20" t="n">
-        <v>453</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>93102</v>
+        <v>289620</v>
       </c>
       <c r="D21" t="n">
-        <v>2468</v>
+        <v>5952</v>
       </c>
       <c r="E21" t="n">
-        <v>385</v>
+        <v>1011</v>
       </c>
       <c r="F21" t="n">
-        <v>294</v>
+        <v>755</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>164352</v>
+        <v>20008</v>
       </c>
       <c r="D22" t="n">
-        <v>3928</v>
+        <v>1144</v>
       </c>
       <c r="E22" t="n">
-        <v>830</v>
+        <v>122</v>
       </c>
       <c r="F22" t="n">
-        <v>241</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>552192</v>
+        <v>124033</v>
       </c>
       <c r="D23" t="n">
-        <v>5948</v>
+        <v>2824</v>
       </c>
       <c r="E23" t="n">
-        <v>830</v>
+        <v>422</v>
       </c>
       <c r="F23" t="n">
-        <v>719</v>
+        <v>383</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>172816</v>
+        <v>66670</v>
       </c>
       <c r="D24" t="n">
-        <v>3988</v>
+        <v>2400</v>
       </c>
       <c r="E24" t="n">
-        <v>859</v>
+        <v>475</v>
       </c>
       <c r="F24" t="n">
-        <v>830</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>68471</v>
+        <v>59430</v>
       </c>
       <c r="D25" t="n">
-        <v>2112</v>
+        <v>2324</v>
       </c>
       <c r="E25" t="n">
-        <v>330</v>
+        <v>493</v>
       </c>
       <c r="F25" t="n">
-        <v>260</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,64 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>34965</v>
+        <v>203712</v>
       </c>
       <c r="D26" t="n">
-        <v>1576</v>
+        <v>4172</v>
       </c>
       <c r="E26" t="n">
-        <v>289</v>
+        <v>651</v>
       </c>
       <c r="F26" t="n">
-        <v>166</v>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>93102</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2468</v>
+      </c>
+      <c r="E27" t="n">
+        <v>385</v>
+      </c>
+      <c r="F27" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>172816</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3988</v>
+      </c>
+      <c r="E28" t="n">
+        <v>859</v>
+      </c>
+      <c r="F28" t="n">
+        <v>830</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/12102.xlsx
+++ b/output/roomself_excel/12102.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>3816</v>
       </c>
-      <c r="E2" t="n">
-        <v>739</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>547</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>438</v>
+      </c>
+      <c r="J2" t="n">
+        <v>43</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +551,38 @@
       <c r="D3" t="n">
         <v>6700</v>
       </c>
-      <c r="E3" t="n">
-        <v>1034</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>1021</v>
+        <v>768</v>
+      </c>
+      <c r="G3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>615</v>
+      </c>
+      <c r="J3" t="n">
+        <v>43</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>360</v>
+      </c>
+      <c r="M3" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +600,31 @@
       <c r="D4" t="n">
         <v>3148</v>
       </c>
-      <c r="E4" t="n">
-        <v>505</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>490</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>446</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +641,23 @@
       <c r="D5" t="n">
         <v>3136</v>
       </c>
-      <c r="E5" t="n">
-        <v>515</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>508</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="G5" t="n">
+        <v>46</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +674,31 @@
       <c r="D6" t="n">
         <v>3180</v>
       </c>
-      <c r="E6" t="n">
-        <v>508</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>505</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="G6" t="n">
+        <v>39</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>159</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +715,23 @@
       <c r="D7" t="n">
         <v>3116</v>
       </c>
-      <c r="E7" t="n">
-        <v>515</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>490</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="G7" t="n">
+        <v>46</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +748,23 @@
       <c r="D8" t="n">
         <v>1992</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>223</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>45</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +781,31 @@
       <c r="D9" t="n">
         <v>1424</v>
       </c>
-      <c r="E9" t="n">
-        <v>270</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>141</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="G9" t="n">
+        <v>54</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>33</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +822,23 @@
       <c r="D10" t="n">
         <v>1536</v>
       </c>
-      <c r="E10" t="n">
-        <v>180</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="G10" t="n">
+        <v>45</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +855,31 @@
       <c r="D11" t="n">
         <v>1576</v>
       </c>
-      <c r="E11" t="n">
-        <v>289</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>166</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>259</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +896,23 @@
       <c r="D12" t="n">
         <v>5520</v>
       </c>
-      <c r="E12" t="n">
-        <v>370</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>362</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="G12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +929,15 @@
       <c r="D13" t="n">
         <v>1268</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +954,23 @@
       <c r="D14" t="n">
         <v>1432</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>124</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>45</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +987,31 @@
       <c r="D15" t="n">
         <v>3928</v>
       </c>
-      <c r="E15" t="n">
-        <v>830</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>241</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="G15" t="n">
+        <v>31</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>768</v>
+      </c>
+      <c r="J15" t="n">
+        <v>27</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1028,31 @@
       <c r="D16" t="n">
         <v>2112</v>
       </c>
-      <c r="E16" t="n">
-        <v>330</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>260</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="G16" t="n">
+        <v>31</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>299</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1069,31 @@
       <c r="D17" t="n">
         <v>5948</v>
       </c>
-      <c r="E17" t="n">
-        <v>830</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>719</v>
-      </c>
+        <v>1438</v>
+      </c>
+      <c r="G17" t="n">
+        <v>31</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>768</v>
+      </c>
+      <c r="J17" t="n">
+        <v>29</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1110,23 @@
       <c r="D18" t="n">
         <v>3092</v>
       </c>
-      <c r="E18" t="n">
-        <v>641</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>266</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="G18" t="n">
+        <v>41</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1143,31 @@
       <c r="D19" t="n">
         <v>1976</v>
       </c>
-      <c r="E19" t="n">
-        <v>332</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>248</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="G19" t="n">
+        <v>41</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>207</v>
+      </c>
+      <c r="J19" t="n">
+        <v>45</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1184,31 @@
       <c r="D20" t="n">
         <v>2396</v>
       </c>
-      <c r="E20" t="n">
-        <v>483</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>161</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>146</v>
+      </c>
+      <c r="J20" t="n">
+        <v>30</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,11 +1225,38 @@
       <c r="D21" t="n">
         <v>5952</v>
       </c>
-      <c r="E21" t="n">
-        <v>1011</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>755</v>
+        <v>396</v>
+      </c>
+      <c r="G21" t="n">
+        <v>42</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>105</v>
+      </c>
+      <c r="J21" t="n">
+        <v>32</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>96</v>
+      </c>
+      <c r="M21" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -915,12 +1274,23 @@
       <c r="D22" t="n">
         <v>1144</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>122</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>45</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1307,31 @@
       <c r="D23" t="n">
         <v>2824</v>
       </c>
-      <c r="E23" t="n">
-        <v>422</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>383</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="G23" t="n">
+        <v>45</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>377</v>
+      </c>
+      <c r="J23" t="n">
+        <v>54</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1348,31 @@
       <c r="D24" t="n">
         <v>2400</v>
       </c>
-      <c r="E24" t="n">
-        <v>475</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>163</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>452</v>
+      </c>
+      <c r="J24" t="n">
+        <v>15</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,11 +1389,38 @@
       <c r="D25" t="n">
         <v>2324</v>
       </c>
-      <c r="E25" t="n">
-        <v>493</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>181</v>
+        <v>134</v>
+      </c>
+      <c r="G25" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>74</v>
+      </c>
+      <c r="J25" t="n">
+        <v>33</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>447</v>
+      </c>
+      <c r="M25" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1003,12 +1438,31 @@
       <c r="D26" t="n">
         <v>4172</v>
       </c>
-      <c r="E26" t="n">
-        <v>651</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>453</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="G26" t="n">
+        <v>31</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>620</v>
+      </c>
+      <c r="J26" t="n">
+        <v>30</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1479,31 @@
       <c r="D27" t="n">
         <v>2468</v>
       </c>
-      <c r="E27" t="n">
-        <v>385</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>294</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="G27" t="n">
+        <v>31</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>263</v>
+      </c>
+      <c r="J27" t="n">
+        <v>31</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1520,31 @@
       <c r="D28" t="n">
         <v>3988</v>
       </c>
-      <c r="E28" t="n">
-        <v>859</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>830</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="G28" t="n">
+        <v>31</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>200</v>
+      </c>
+      <c r="J28" t="n">
+        <v>31</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
